--- a/dPlacares.xlsx
+++ b/dPlacares.xlsx
@@ -413,1917 +413,2502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID_PARTIDA</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Competição</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ID_CAMPEONATO</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Adversário</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>ID_TIME</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>RESULTADO</t>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Placar Adversário</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Placar Botafogo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026.02.01-CAMCA4-5</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>3FLBRRJ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>01/02/2026</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026.04.01-CAMBR2-9</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>26MIBRSP</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025.10.01-CAMBR2-26</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>20BABRBA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>01/10/2025</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024.05.02-CAMCO3-3° FASE</t>
+          <t>02/05/2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>CAMCO3</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>22VIBRBA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>02/05/2024</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024.04.03-CAMLI5-FG</t>
+          <t>03/04/2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Junior de Barranquilla</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>85JUCOBA</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>03/04/2024</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025.08.03-CAMBR2-18</t>
+          <t>03/08/2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>16CRBRMG</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>03/08/2025</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025.06.04-CAMBR2-10</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>23CEBRCE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>04/06/2025</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025.04.05-CAMBR2-2</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>121JUBRCS</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>05/04/2025</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024.05.05-CAMBR2-5</t>
+          <t>05/05/2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>20BABRBA</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>05/05/2024</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024.11.05-CAMBR2-32</t>
+          <t>05/11/2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>4VABRRJ</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>05/11/2024</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025.11.05-CAMBR2-32</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>4VABRRJ</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>05/11/2025</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024.03.06-CAMLI5-3° FASE</t>
+          <t>06/03/2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>9REBRSP</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>06/03/2024</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026.03.07-CAMCA4-FINAL - TR</t>
+          <t>07/03/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bangu</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>40BABRRJ</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>07/03/2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024.07.07-CAMBR2-15</t>
+          <t>07/07/2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>15ATBRMG</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>07/07/2024</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025.12.07-CAMBR2-38</t>
+          <t>07/12/2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>21FOBRCE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>07/12/2025</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025.04.08-CAMLI5-2</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carabobo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>118CAVEVA</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>08/04/2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2024.05.08-CAMLI5-FG</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>91LDECQU</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>08/05/2024</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024.12.08-CAMBR2-38</t>
+          <t>08/12/2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>6SÃBRSP</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>08/12/2024</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026.04.09-CAMSU6-FG</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Sulamericana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>CAMSU6</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>115CAVECA</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024.11.09-CAMBR2-33</t>
+          <t>09/11/2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>24CUBRMT</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>09/11/2024</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026.03.10-CAMLI5-3° Fase</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Barcelona de Guayaquil</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>93BAECGU</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>10/03/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025.01.11-CAMCA4-1</t>
+          <t>11/01/2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Maricá</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>41MABRRJ</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>11/01/2025</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025.05.11-CAMBR2-8</t>
+          <t>11/05/2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>11INBRRS</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>11/05/2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024.06.11-CAMBR2-8</t>
+          <t>11/06/2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>3FLBRRJ</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>11/06/2024</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025.09.11-CAMCO3-QUARTAS</t>
+          <t>11/09/2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>CAMCO3</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>4VABRRJ</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>11/09/2025</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026.04.12-CAMBR2-11</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>12COBRPR</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025.01.14-CAMCA4-2</t>
+          <t>14/01/2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Portuguesa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>37POBRRJ</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>14/01/2025</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026.03.14-CAMBR2-6</t>
+          <t>14/03/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>2FLBRRJ</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>14/03/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025.05.14-CAMLI5-5</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Estudiantes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>51ESARLP</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>14/05/2025</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024.08.14-CAMLI5-OITAVAS</t>
+          <t>14/08/2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>5PABRSP</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>14/08/2024</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025.08.14-CAMLI5-OITAVAS</t>
+          <t>14/08/2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>91LDECQU</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>14/08/2025</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024.09.14-CAMBR2-26</t>
+          <t>14/09/2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>8COBRSP</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>14/09/2024</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026.02.15-CAMCA4-Quartas</t>
+          <t>15/02/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>2FLBRRJ</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>15/02/2026</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025.10.15-CAMBR2-28</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>2FLBRRJ</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025.04.16-CAMBR2-4</t>
+          <t>16/04/2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>6SÃBRSP</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>16/04/2025</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025.07.16-CAMBR2-14</t>
+          <t>16/07/2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>22VIBRBA</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>16/07/2025</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024.01.17-CAMCA4-1</t>
+          <t>17/01/2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Madureira</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>43MABRRJ</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>17/01/2024</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024.03.17-CAMCA4-SF</t>
+          <t>17/03/2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sampaio Corrêa</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>38SABRRJ</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>17/03/2024</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024.07.17-CAMBR2-17</t>
+          <t>17/07/2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>5PABRSP</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>17/07/2024</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025.08.17-CAMBR2-20</t>
+          <t>17/08/2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>5PABRSP</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>17/08/2025</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025.09.17-CAMBR2-12</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>26MIBRSP</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>17/09/2025</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024.02.18-CAMCA4-9</t>
+          <t>18/02/2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>4VABRRJ</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>18/02/2024</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024.04.18-CAMBR2-2</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Atlético-GO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>17ATBRGO</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>18/04/2024</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024.08.18-CAMBR2-23</t>
+          <t>18/08/2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>2FLBRRJ</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>18/08/2024</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024.09.18-CAMLI5-QUARTAS</t>
+          <t>18/09/2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>6SÃBRSP</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>18/09/2024</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024.10.18-CAMBR2-30</t>
+          <t>18/10/2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>25CRBRSC</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>18/10/2024</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025.11.18-CAMBR2-34</t>
+          <t>18/11/2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>13SPBRPE</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>18/11/2025</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024.06.19-CAMBR2-10</t>
+          <t>19/06/2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Athlético</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>14ATBRPR</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>19/06/2024</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024.01.20-CAMCA4-2</t>
+          <t>20/01/2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bangu</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>40BABRRJ</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>20/01/2024</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024.07.20-CAMBR2-18</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>11INBRRS</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>20/07/2024</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025.09.20-CAMBR2-24</t>
+          <t>20/09/2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>15ATBRMG</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>20/09/2025</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026.01.21-CAMCA4-3</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>36VOBRRJ</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>21/01/2026</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024.04.21-CAMBR2-3</t>
+          <t>21/04/2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>121JUBRCS</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>21/04/2024</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025.01.22-CAMCA4-4</t>
+          <t>22/01/2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>36VOBRRJ</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>22/01/2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025.11.22-CAMBR2-35</t>
+          <t>22/11/2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>10GRBRRS</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>22/11/2025</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024.10.23-CAMLI5-SEMIS</t>
+          <t>23/10/2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>109PEUYMO</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>23/10/2024</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024.11.23-CAMBR2-35</t>
+          <t>23/11/2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>22VIBRBA</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>23/11/2024</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026.01.24-CAMCA4-4</t>
+          <t>24/01/2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Bangu</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>40BABRRJ</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>24/01/2026</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024.04.24-CAMLI5-FG</t>
+          <t>24/04/2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>103UNPELI</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>24/04/2024</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026.02.25-CAMLI5-2° FASE</t>
+          <t>25/02/2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nacional de Potosí</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>123NABOPO</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>25/02/2026</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024.09.25-CAMLI5-QUARTAS</t>
+          <t>25/09/2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>6SÃBRSP</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>25/09/2024</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025.01.26-CAMCA4-5</t>
+          <t>26/01/2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Bangu</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>40BABRRJ</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>26/01/2025</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025.04.26-CAMBR2-6</t>
+          <t>26/04/2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>3FLBRRJ</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>26/04/2025</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024.06.26-CAMBR2-12</t>
+          <t>26/06/2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>9REBRSP</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>26/06/2024</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025.07.26-CAMBR2-17</t>
+          <t>26/07/2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>8COBRSP</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>26/07/2025</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025.10.26-CAMBR2-30</t>
+          <t>26/10/2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>7SABRSP</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>26/10/2025</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024.01.27-CAMCA4-4</t>
+          <t>27/01/2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sampaio Corrêa</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>38SABRRJ</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>27/01/2024</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025.02.27-CAMRE10-FINAL</t>
+          <t>27/02/2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>Recopa</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>CAMRE10</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Racing</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>63RAARAV</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>27/02/2025</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025.05.27-CAMLI5-6</t>
+          <t>27/05/2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>78UNCLSA</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>27/05/2025</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2024.07.27-CAMBR2-20</t>
+          <t>27/07/2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>16CRBRMG</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>27/07/2024</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2024.02.28-CAMLI5-2° FASE</t>
+          <t>28/02/2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>74AUBOCO</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>28/02/2024</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026.02.28-CAMCA4-SEMIS - TR</t>
+          <t>28/02/2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Boavista</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>44BOBRRJ</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025.01.29-CAMCA4-6</t>
+          <t>29/01/2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>3FLBRRJ</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>29/01/2025</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026.01.29-CAMBR2-1</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>16CRBRMG</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>29/01/2026</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025.07.29-CAMCO3-OITAVAS</t>
+          <t>29/07/2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
+          <t>Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
           <t>CAMCO3</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>9REBRSP</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>29/07/2025</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2024.01.30-CAMCA4-5</t>
+          <t>30/01/2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Portuguesa</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>37POBRRJ</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>30/01/2024</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025.04.30-CAMCO3-3° FASE</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
           <t>CAMCO3</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>122CABRDF</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>30/04/2025</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2024.07.30-CAMCO3-OITAVAS</t>
+          <t>30/07/2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
+          <t>Copa do Brasil</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
           <t>CAMCO3</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>20BABRBA</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>30/07/2024</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025.08.30-CAMBR2-22</t>
+          <t>30/08/2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>9REBRSP</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>30/08/2025</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024.10.30-CAMLI5-SEMIS</t>
+          <t>30/10/2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>Libertadores</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>CAMLI5</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>109PEUYMO</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>30/10/2024</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2024.03.31-CAMCA4-FI</t>
+          <t>31/03/2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>Carioca</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
           <t>CAMCA4</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Boavista</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>44BOBRRJ</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>31/03/2024</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024.08.31-CAMBR2-25</t>
+          <t>31/08/2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CAMBR2</t>
+          <t>Brasileirão</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>CAMBR2</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>21FOBRCE</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>31/08/2024</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dPlacares.xlsx
+++ b/dPlacares.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F813B61F-9670-42F1-8555-B78B55D4625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="519" documentId="8_{F813B61F-9670-42F1-8555-B78B55D4625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{772E36AA-D24A-4619-8D5B-AA3734D1ECE3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6666F575-2A8C-4CCA-9598-CF178E39A238}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$I$172</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="138">
   <si>
     <t>Data</t>
   </si>
@@ -441,6 +441,18 @@
   </si>
   <si>
     <t>115CAVECA</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
@@ -476,9 +488,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBC53B6-4B60-44A2-8CF3-BAC076789A26}">
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
@@ -826,7 +840,7 @@
     <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -851,8 +865,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45637</v>
       </c>
@@ -877,8 +894,11 @@
       <c r="H2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45634</v>
       </c>
@@ -903,8 +923,11 @@
       <c r="H3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45630</v>
       </c>
@@ -929,8 +952,11 @@
       <c r="H4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45626</v>
       </c>
@@ -955,8 +981,11 @@
       <c r="H5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45622</v>
       </c>
@@ -981,8 +1010,11 @@
       <c r="H6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>45619</v>
       </c>
@@ -1007,9 +1039,12 @@
       <c r="H7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="I7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>45616</v>
       </c>
       <c r="B8" t="s">
@@ -1033,9 +1068,12 @@
       <c r="H8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="I8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>45605</v>
       </c>
       <c r="B9" t="s">
@@ -1059,9 +1097,12 @@
       <c r="H9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="I9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>45601</v>
       </c>
       <c r="B10" t="s">
@@ -1085,9 +1126,12 @@
       <c r="H10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="I10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>45595</v>
       </c>
       <c r="B11" t="s">
@@ -1111,9 +1155,12 @@
       <c r="H11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="I11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>45591</v>
       </c>
       <c r="B12" t="s">
@@ -1137,9 +1184,12 @@
       <c r="H12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="I12" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>45588</v>
       </c>
       <c r="B13" t="s">
@@ -1163,9 +1213,12 @@
       <c r="H13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+      <c r="I13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>45583</v>
       </c>
       <c r="B14" t="s">
@@ -1189,9 +1242,12 @@
       <c r="H14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+      <c r="I14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>45570</v>
       </c>
       <c r="B15" t="s">
@@ -1215,9 +1271,12 @@
       <c r="H15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="I15" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>45563</v>
       </c>
       <c r="B16" t="s">
@@ -1241,9 +1300,12 @@
       <c r="H16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="I16" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>45560</v>
       </c>
       <c r="B17" t="s">
@@ -1267,9 +1329,12 @@
       <c r="H17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="I17" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>45556</v>
       </c>
       <c r="B18" t="s">
@@ -1293,9 +1358,12 @@
       <c r="H18" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="I18" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>45553</v>
       </c>
       <c r="B19" t="s">
@@ -1319,9 +1387,12 @@
       <c r="H19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+      <c r="I19" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>45549</v>
       </c>
       <c r="B20" t="s">
@@ -1345,9 +1416,12 @@
       <c r="H20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+      <c r="I20" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>45535</v>
       </c>
       <c r="B21" t="s">
@@ -1371,9 +1445,12 @@
       <c r="H21" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
+      <c r="I21" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>45529</v>
       </c>
       <c r="B22" t="s">
@@ -1397,9 +1474,12 @@
       <c r="H22" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+      <c r="I22" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>45525</v>
       </c>
       <c r="B23" t="s">
@@ -1423,9 +1503,12 @@
       <c r="H23" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+      <c r="I23" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>45522</v>
       </c>
       <c r="B24" t="s">
@@ -1449,9 +1532,12 @@
       <c r="H24" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+      <c r="I24" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>45518</v>
       </c>
       <c r="B25" t="s">
@@ -1475,9 +1561,12 @@
       <c r="H25" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="I25" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>45515</v>
       </c>
       <c r="B26" t="s">
@@ -1501,9 +1590,12 @@
       <c r="H26" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+      <c r="I26" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>45511</v>
       </c>
       <c r="B27" t="s">
@@ -1527,9 +1619,12 @@
       <c r="H27" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
+      <c r="I27" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>45507</v>
       </c>
       <c r="B28" t="s">
@@ -1553,9 +1648,12 @@
       <c r="H28" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+      <c r="I28" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>45503</v>
       </c>
       <c r="B29" t="s">
@@ -1579,9 +1677,12 @@
       <c r="H29" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="I29" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>45500</v>
       </c>
       <c r="B30" t="s">
@@ -1605,9 +1706,12 @@
       <c r="H30" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+      <c r="I30" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>45497</v>
       </c>
       <c r="B31" t="s">
@@ -1631,9 +1735,12 @@
       <c r="H31" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+      <c r="I31" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>45493</v>
       </c>
       <c r="B32" t="s">
@@ -1657,9 +1764,12 @@
       <c r="H32" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+      <c r="I32" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>45490</v>
       </c>
       <c r="B33" t="s">
@@ -1683,9 +1793,12 @@
       <c r="H33" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
+      <c r="I33" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>45484</v>
       </c>
       <c r="B34" t="s">
@@ -1709,9 +1822,12 @@
       <c r="H34" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
+      <c r="I34" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>45480</v>
       </c>
       <c r="B35" t="s">
@@ -1735,9 +1851,12 @@
       <c r="H35" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+      <c r="I35" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>45476</v>
       </c>
       <c r="B36" t="s">
@@ -1761,9 +1880,12 @@
       <c r="H36" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+      <c r="I36" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>45472</v>
       </c>
       <c r="B37" t="s">
@@ -1787,9 +1909,12 @@
       <c r="H37" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
+      <c r="I37" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>45469</v>
       </c>
       <c r="B38" t="s">
@@ -1813,9 +1938,12 @@
       <c r="H38" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
+      <c r="I38" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>45465</v>
       </c>
       <c r="B39" t="s">
@@ -1839,9 +1967,12 @@
       <c r="H39" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
+      <c r="I39" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>45462</v>
       </c>
       <c r="B40" t="s">
@@ -1865,9 +1996,12 @@
       <c r="H40" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+      <c r="I40" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>45459</v>
       </c>
       <c r="B41" t="s">
@@ -1891,10 +2025,13 @@
       <c r="H41" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
-        <v>45619</v>
+      <c r="I41" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>45454</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -1917,10 +2054,13 @@
       <c r="H42" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
-        <v>45616</v>
+      <c r="I42" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>45444</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -1943,10 +2083,13 @@
       <c r="H43" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
-        <v>45605</v>
+      <c r="I43" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>45440</v>
       </c>
       <c r="B44" t="s">
         <v>20</v>
@@ -1969,10 +2112,13 @@
       <c r="H44" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
-        <v>45601</v>
+      <c r="I44" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
+        <v>45434</v>
       </c>
       <c r="B45" t="s">
         <v>55</v>
@@ -1995,10 +2141,13 @@
       <c r="H45" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
-        <v>45595</v>
+      <c r="I45" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>45428</v>
       </c>
       <c r="B46" t="s">
         <v>20</v>
@@ -2021,10 +2170,13 @@
       <c r="H46" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
-        <v>45591</v>
+      <c r="I46" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
+        <v>45424</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -2047,10 +2199,13 @@
       <c r="H47" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
-        <v>45588</v>
+      <c r="I47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
+        <v>45420</v>
       </c>
       <c r="B48" t="s">
         <v>20</v>
@@ -2073,10 +2228,13 @@
       <c r="H48" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
-        <v>45583</v>
+      <c r="I48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
+        <v>45417</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -2099,10 +2257,13 @@
       <c r="H49" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
-        <v>45570</v>
+      <c r="I49" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
+        <v>45414</v>
       </c>
       <c r="B50" t="s">
         <v>55</v>
@@ -2125,10 +2286,13 @@
       <c r="H50" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
-        <v>45563</v>
+      <c r="I50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
+        <v>45410</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -2151,10 +2315,13 @@
       <c r="H51" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
-        <v>45560</v>
+      <c r="I51" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>45406</v>
       </c>
       <c r="B52" t="s">
         <v>20</v>
@@ -2177,10 +2344,13 @@
       <c r="H52" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
-        <v>45556</v>
+      <c r="I52" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>45403</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -2203,10 +2373,13 @@
       <c r="H53" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
-        <v>45553</v>
+      <c r="I53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>45400</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -2229,36 +2402,42 @@
       <c r="H54" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
-        <v>45549</v>
+      <c r="I54" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>45393</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E55" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
-        <v>45535</v>
+      <c r="I55" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>45385</v>
       </c>
       <c r="B56" t="s">
         <v>20</v>
@@ -2267,50 +2446,56 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
-        <v>45529</v>
+      <c r="I56" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>45382</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
-        <v>45525</v>
+        <v>17</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>45378</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
@@ -2328,15 +2513,18 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
-        <v>45522</v>
+      <c r="I58" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>45368</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
@@ -2345,50 +2533,56 @@
         <v>68</v>
       </c>
       <c r="D59" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E59" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
-        <v>45518</v>
+      <c r="I59" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>45365</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E60" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
-        <v>45515</v>
+        <v>12</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>45364</v>
       </c>
       <c r="B61" t="s">
         <v>20</v>
@@ -2411,10 +2605,13 @@
       <c r="H61" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
-        <v>45511</v>
+      <c r="I61" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>45361</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
@@ -2437,10 +2634,13 @@
       <c r="H62" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
-        <v>45507</v>
+      <c r="I62" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>45357</v>
       </c>
       <c r="B63" t="s">
         <v>20</v>
@@ -2463,10 +2663,13 @@
       <c r="H63" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
-        <v>45503</v>
+      <c r="I63" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>45354</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -2489,10 +2692,13 @@
       <c r="H64" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
-        <v>45500</v>
+      <c r="I64" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>45350</v>
       </c>
       <c r="B65" t="s">
         <v>20</v>
@@ -2515,10 +2721,13 @@
       <c r="H65" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
-        <v>45497</v>
+      <c r="I65" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>45346</v>
       </c>
       <c r="B66" t="s">
         <v>67</v>
@@ -2541,10 +2750,13 @@
       <c r="H66" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
-        <v>45493</v>
+      <c r="I66" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>45343</v>
       </c>
       <c r="B67" t="s">
         <v>20</v>
@@ -2567,10 +2779,13 @@
       <c r="H67" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
-        <v>45490</v>
+      <c r="I67" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
+        <v>45340</v>
       </c>
       <c r="B68" t="s">
         <v>67</v>
@@ -2593,10 +2808,13 @@
       <c r="H68" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
-        <v>45484</v>
+      <c r="I68" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>45336</v>
       </c>
       <c r="B69" t="s">
         <v>67</v>
@@ -2619,10 +2837,13 @@
       <c r="H69" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="1">
-        <v>45480</v>
+      <c r="I69" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
+        <v>45329</v>
       </c>
       <c r="B70" t="s">
         <v>67</v>
@@ -2645,10 +2866,13 @@
       <c r="H70" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="1">
-        <v>45476</v>
+      <c r="I70" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
+        <v>45325</v>
       </c>
       <c r="B71" t="s">
         <v>67</v>
@@ -2671,10 +2895,13 @@
       <c r="H71" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="1">
-        <v>45472</v>
+      <c r="I71" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
+        <v>45321</v>
       </c>
       <c r="B72" t="s">
         <v>67</v>
@@ -2697,10 +2924,13 @@
       <c r="H72" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="1">
-        <v>45469</v>
+      <c r="I72" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
+        <v>45318</v>
       </c>
       <c r="B73" t="s">
         <v>67</v>
@@ -2723,10 +2953,13 @@
       <c r="H73" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A74" s="1">
-        <v>45465</v>
+      <c r="I73" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
+        <v>45315</v>
       </c>
       <c r="B74" t="s">
         <v>67</v>
@@ -2749,10 +2982,13 @@
       <c r="H74" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A75" s="1">
-        <v>45462</v>
+      <c r="I74" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
+        <v>45311</v>
       </c>
       <c r="B75" t="s">
         <v>67</v>
@@ -2775,10 +3011,13 @@
       <c r="H75" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A76" s="1">
-        <v>45459</v>
+      <c r="I75" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
+        <v>45308</v>
       </c>
       <c r="B76" t="s">
         <v>67</v>
@@ -2801,308 +3040,344 @@
       <c r="H76" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I76" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
-        <v>45998</v>
+        <v>45668</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="E77" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="F77">
         <v>2</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I77" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
-        <v>45995</v>
+        <v>45671</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E78" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G78">
         <v>2</v>
       </c>
       <c r="H78" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" s="1">
+        <v>45675</v>
+      </c>
+      <c r="B79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" t="s">
+        <v>71</v>
+      </c>
+      <c r="E79" t="s">
+        <v>72</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
+        <v>45679</v>
+      </c>
+      <c r="B80" t="s">
+        <v>117</v>
+      </c>
+      <c r="C80" t="s">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" t="s">
+        <v>78</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" s="1">
+        <v>45683</v>
+      </c>
+      <c r="B81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" t="s">
+        <v>84</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" s="1">
+        <v>45686</v>
+      </c>
+      <c r="B82" t="s">
+        <v>117</v>
+      </c>
+      <c r="C82" t="s">
+        <v>68</v>
+      </c>
+      <c r="D82" t="s">
+        <v>43</v>
+      </c>
+      <c r="E82" t="s">
+        <v>44</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" s="1">
+        <v>45690</v>
+      </c>
+      <c r="B83" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" t="s">
+        <v>119</v>
+      </c>
+      <c r="D83" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" t="s">
+        <v>52</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" s="1">
+        <v>45694</v>
+      </c>
+      <c r="B84" t="s">
+        <v>117</v>
+      </c>
+      <c r="C84" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" t="s">
+        <v>79</v>
+      </c>
+      <c r="E84" t="s">
+        <v>80</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" s="1">
+        <v>45697</v>
+      </c>
+      <c r="B85" t="s">
+        <v>117</v>
+      </c>
+      <c r="C85" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" t="s">
+        <v>85</v>
+      </c>
+      <c r="E85" t="s">
+        <v>86</v>
+      </c>
+      <c r="F85">
+        <v>2</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
+        <v>45700</v>
+      </c>
+      <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" t="s">
+        <v>51</v>
+      </c>
+      <c r="E86" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
+        <v>45703</v>
+      </c>
+      <c r="B87" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" t="s">
+        <v>70</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B79" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>45</v>
-      </c>
-      <c r="E79" t="s">
-        <v>46</v>
-      </c>
-      <c r="F79">
-        <v>2</v>
-      </c>
-      <c r="G79">
-        <v>2</v>
-      </c>
-      <c r="H79" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" s="1">
-        <v>45983</v>
-      </c>
-      <c r="B80" t="s">
-        <v>87</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
-      </c>
-      <c r="D80" t="s">
-        <v>41</v>
-      </c>
-      <c r="E80" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80">
-        <v>2</v>
-      </c>
-      <c r="G80">
-        <v>3</v>
-      </c>
-      <c r="H80" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A81" s="1">
-        <v>45979</v>
-      </c>
-      <c r="B81" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>88</v>
-      </c>
-      <c r="E81" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81">
-        <v>2</v>
-      </c>
-      <c r="G81">
-        <v>3</v>
-      </c>
-      <c r="H81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A82" s="1">
-        <v>45970</v>
-      </c>
-      <c r="B82" t="s">
-        <v>87</v>
-      </c>
-      <c r="C82" t="s">
-        <v>14</v>
-      </c>
-      <c r="D82" t="s">
-        <v>26</v>
-      </c>
-      <c r="E82" t="s">
-        <v>27</v>
-      </c>
-      <c r="F82">
-        <v>0</v>
-      </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A83" s="1">
-        <v>45966</v>
-      </c>
-      <c r="B83" t="s">
-        <v>87</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>31</v>
-      </c>
-      <c r="E83" t="s">
-        <v>32</v>
-      </c>
-      <c r="F83">
-        <v>0</v>
-      </c>
-      <c r="G83">
-        <v>3</v>
-      </c>
-      <c r="H83" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="1">
-        <v>45962</v>
-      </c>
-      <c r="B84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C84" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" t="s">
-        <v>90</v>
-      </c>
-      <c r="E84" t="s">
-        <v>91</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-      <c r="H84" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="1">
-        <v>45956</v>
-      </c>
-      <c r="B85" t="s">
-        <v>87</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>92</v>
-      </c>
-      <c r="E85" t="s">
-        <v>93</v>
-      </c>
-      <c r="F85">
-        <v>2</v>
-      </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
-      <c r="H85" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="1">
-        <v>45949</v>
-      </c>
-      <c r="B86" t="s">
-        <v>87</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>94</v>
-      </c>
-      <c r="E86" t="s">
-        <v>95</v>
-      </c>
-      <c r="F86">
-        <v>0</v>
-      </c>
-      <c r="G86">
-        <v>2</v>
-      </c>
-      <c r="H86" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="1">
-        <v>45945</v>
-      </c>
-      <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>51</v>
-      </c>
-      <c r="E87" t="s">
-        <v>52</v>
-      </c>
-      <c r="F87">
-        <v>3</v>
-      </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
-      <c r="H87" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I87" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
-        <v>45934</v>
+        <v>45708</v>
       </c>
       <c r="B88" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -3113,48 +3388,54 @@
       <c r="H88" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I88" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
-        <v>45931</v>
+        <v>45711</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D89" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="E89" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I89" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
-        <v>45928</v>
+        <v>45715</v>
       </c>
       <c r="B90" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="F90">
         <v>2</v>
@@ -3165,10 +3446,13 @@
       <c r="H90" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I90" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
-        <v>45924</v>
+        <v>45746</v>
       </c>
       <c r="B91" t="s">
         <v>87</v>
@@ -3177,50 +3461,56 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I91" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
-        <v>45920</v>
+        <v>45749</v>
       </c>
       <c r="B92" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="E92" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="F92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I92" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
-        <v>45917</v>
+        <v>45752</v>
       </c>
       <c r="B93" t="s">
         <v>87</v>
@@ -3229,76 +3519,85 @@
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="E93" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I93" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
-        <v>45914</v>
+        <v>45755</v>
       </c>
       <c r="B94" t="s">
+        <v>97</v>
+      </c>
+      <c r="C94" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" t="s">
+        <v>111</v>
+      </c>
+      <c r="E94" t="s">
+        <v>112</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="H94" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" s="1">
+        <v>45759</v>
+      </c>
+      <c r="B95" t="s">
         <v>87</v>
       </c>
-      <c r="C94" t="s">
-        <v>14</v>
-      </c>
-      <c r="D94" t="s">
-        <v>15</v>
-      </c>
-      <c r="E94" t="s">
-        <v>16</v>
-      </c>
-      <c r="F94">
-        <v>1</v>
-      </c>
-      <c r="G94">
-        <v>0</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" t="s">
+        <v>36</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A95" s="1">
-        <v>45911</v>
-      </c>
-      <c r="B95" t="s">
-        <v>96</v>
-      </c>
-      <c r="C95" t="s">
-        <v>56</v>
-      </c>
-      <c r="D95" t="s">
-        <v>31</v>
-      </c>
-      <c r="E95" t="s">
-        <v>32</v>
-      </c>
-      <c r="F95">
-        <v>1</v>
-      </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-      <c r="H95" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I95" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
-        <v>45899</v>
+        <v>45763</v>
       </c>
       <c r="B96" t="s">
         <v>87</v>
@@ -3307,154 +3606,172 @@
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E96" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96" t="s">
+        <v>28</v>
+      </c>
+      <c r="I96" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" s="1">
+        <v>45767</v>
+      </c>
+      <c r="B97" t="s">
+        <v>87</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" t="s">
+        <v>22</v>
+      </c>
+      <c r="E97" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98" s="1">
+        <v>45770</v>
+      </c>
+      <c r="B98" t="s">
+        <v>97</v>
+      </c>
+      <c r="C98" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" t="s">
+        <v>109</v>
+      </c>
+      <c r="E98" t="s">
+        <v>110</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99" s="1">
+        <v>45773</v>
+      </c>
+      <c r="B99" t="s">
+        <v>87</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" t="s">
+        <v>44</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>2</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100" s="2">
+        <v>45775</v>
+      </c>
+      <c r="B100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" t="s">
+        <v>51</v>
+      </c>
+      <c r="E100" t="s">
+        <v>52</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" s="1">
+        <v>45777</v>
+      </c>
+      <c r="B101" t="s">
+        <v>96</v>
+      </c>
+      <c r="C101" t="s">
+        <v>56</v>
+      </c>
+      <c r="D101" t="s">
+        <v>107</v>
+      </c>
+      <c r="E101" t="s">
+        <v>108</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
         <v>4</v>
       </c>
-      <c r="H96" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="1">
-        <v>45896</v>
-      </c>
-      <c r="B97" t="s">
-        <v>96</v>
-      </c>
-      <c r="C97" t="s">
-        <v>56</v>
-      </c>
-      <c r="D97" t="s">
-        <v>31</v>
-      </c>
-      <c r="E97" t="s">
-        <v>32</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
-      </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-      <c r="H97" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" s="1">
-        <v>45893</v>
-      </c>
-      <c r="B98" t="s">
-        <v>87</v>
-      </c>
-      <c r="C98" t="s">
-        <v>14</v>
-      </c>
-      <c r="D98" t="s">
-        <v>53</v>
-      </c>
-      <c r="E98" t="s">
-        <v>54</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98">
-        <v>3</v>
-      </c>
-      <c r="H98" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="1">
-        <v>45890</v>
-      </c>
-      <c r="B99" t="s">
-        <v>97</v>
-      </c>
-      <c r="C99" t="s">
-        <v>21</v>
-      </c>
-      <c r="D99" t="s">
-        <v>65</v>
-      </c>
-      <c r="E99" t="s">
-        <v>66</v>
-      </c>
-      <c r="F99">
-        <v>2</v>
-      </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
-      <c r="H99" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A100" s="1">
-        <v>45886</v>
-      </c>
-      <c r="B100" t="s">
-        <v>87</v>
-      </c>
-      <c r="C100" t="s">
-        <v>14</v>
-      </c>
-      <c r="D100" t="s">
-        <v>24</v>
-      </c>
-      <c r="E100" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100">
-        <v>1</v>
-      </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
-      <c r="H100" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A101" s="1">
-        <v>45883</v>
-      </c>
-      <c r="B101" t="s">
-        <v>97</v>
-      </c>
-      <c r="C101" t="s">
-        <v>21</v>
-      </c>
-      <c r="D101" t="s">
-        <v>65</v>
-      </c>
-      <c r="E101" t="s">
-        <v>66</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
       <c r="H101" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I101" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
-        <v>45878</v>
+        <v>45780</v>
       </c>
       <c r="B102" t="s">
         <v>87</v>
@@ -3463,50 +3780,56 @@
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E102" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H102" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I102" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
-        <v>45875</v>
+        <v>45783</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C103" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D103" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E103" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I103" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
-        <v>45872</v>
+        <v>45788</v>
       </c>
       <c r="B104" t="s">
         <v>87</v>
@@ -3515,50 +3838,56 @@
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="F104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H104" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I104" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
-        <v>45867</v>
+        <v>45791</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D105" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="E105" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I105" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
-        <v>45864</v>
+        <v>45795</v>
       </c>
       <c r="B106" t="s">
         <v>87</v>
@@ -3567,76 +3896,85 @@
         <v>14</v>
       </c>
       <c r="D106" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E106" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I106" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
-        <v>45858</v>
+        <v>45799</v>
       </c>
       <c r="B107" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D107" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="E107" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I107" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
-        <v>45854</v>
+        <v>45804</v>
       </c>
       <c r="B108" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C108" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D108" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="E108" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="F108">
         <v>0</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I108" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
-        <v>45850</v>
+        <v>45809</v>
       </c>
       <c r="B109" t="s">
         <v>87</v>
@@ -3645,50 +3983,56 @@
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="E109" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="F109">
         <v>0</v>
       </c>
       <c r="G109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I109" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
-        <v>45836</v>
+        <v>45812</v>
       </c>
       <c r="B110" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C110" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="E110" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H110" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I110" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
-        <v>45831</v>
+        <v>45823</v>
       </c>
       <c r="B111" t="s">
         <v>98</v>
@@ -3697,22 +4041,25 @@
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E111" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I111" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>45827</v>
       </c>
@@ -3737,10 +4084,13 @@
       <c r="H112" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I112" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
-        <v>45823</v>
+        <v>45831</v>
       </c>
       <c r="B113" t="s">
         <v>98</v>
@@ -3749,50 +4099,56 @@
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E113" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I113" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
-        <v>45812</v>
+        <v>45836</v>
       </c>
       <c r="B114" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="E114" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G114">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H114" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I114" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
-        <v>45809</v>
+        <v>45850</v>
       </c>
       <c r="B115" t="s">
         <v>87</v>
@@ -3801,76 +4157,85 @@
         <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="E115" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="F115">
         <v>0</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I115" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
-        <v>45804</v>
+        <v>45854</v>
       </c>
       <c r="B116" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="E116" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="F116">
         <v>0</v>
       </c>
       <c r="G116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I116" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
-        <v>45799</v>
+        <v>45858</v>
       </c>
       <c r="B117" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C117" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="E117" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
-        <v>45795</v>
+        <v>45864</v>
       </c>
       <c r="B118" t="s">
         <v>87</v>
@@ -3879,50 +4244,56 @@
         <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E118" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I118" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
-        <v>45791</v>
+        <v>45867</v>
       </c>
       <c r="B119" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C119" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D119" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="E119" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="F119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I119" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
-        <v>45788</v>
+        <v>45872</v>
       </c>
       <c r="B120" t="s">
         <v>87</v>
@@ -3931,50 +4302,56 @@
         <v>14</v>
       </c>
       <c r="D120" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E120" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G120">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H120" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I120" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
-        <v>45783</v>
+        <v>45875</v>
       </c>
       <c r="B121" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C121" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D121" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="E121" t="s">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I121" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
-        <v>45780</v>
+        <v>45878</v>
       </c>
       <c r="B122" t="s">
         <v>87</v>
@@ -3983,50 +4360,56 @@
         <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E122" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H122" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
-        <v>45777</v>
+        <v>45883</v>
       </c>
       <c r="B123" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C123" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D123" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="E123" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I123" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
-        <v>45773</v>
+        <v>45886</v>
       </c>
       <c r="B124" t="s">
         <v>87</v>
@@ -4035,24 +4418,27 @@
         <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E124" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I124" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
-        <v>45770</v>
+        <v>45890</v>
       </c>
       <c r="B125" t="s">
         <v>97</v>
@@ -4061,13 +4447,13 @@
         <v>21</v>
       </c>
       <c r="D125" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="E125" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -4075,10 +4461,13 @@
       <c r="H125" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I125" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
-        <v>45767</v>
+        <v>45893</v>
       </c>
       <c r="B126" t="s">
         <v>87</v>
@@ -4087,50 +4476,56 @@
         <v>14</v>
       </c>
       <c r="D126" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="E126" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F126">
         <v>1</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H126" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
-        <v>45763</v>
+        <v>45896</v>
       </c>
       <c r="B127" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C127" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="D127" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E127" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I127" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
-        <v>45759</v>
+        <v>45899</v>
       </c>
       <c r="B128" t="s">
         <v>87</v>
@@ -4148,41 +4543,47 @@
         <v>1</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H128" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
-        <v>45755</v>
+        <v>45911</v>
       </c>
       <c r="B129" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C129" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D129" t="s">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="E129" t="s">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H129" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I129" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
-        <v>45752</v>
+        <v>45914</v>
       </c>
       <c r="B130" t="s">
         <v>87</v>
@@ -4191,50 +4592,56 @@
         <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="E130" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I130" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
-        <v>45749</v>
+        <v>45917</v>
       </c>
       <c r="B131" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D131" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="E131" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H131" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I131" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
-        <v>45746</v>
+        <v>45920</v>
       </c>
       <c r="B132" t="s">
         <v>87</v>
@@ -4243,65 +4650,71 @@
         <v>14</v>
       </c>
       <c r="D132" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E132" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F132">
         <v>0</v>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="1">
+        <v>45924</v>
+      </c>
+      <c r="B133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C133" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133" t="s">
+        <v>41</v>
+      </c>
+      <c r="E133" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A133" s="1">
-        <v>45715</v>
-      </c>
-      <c r="B133" t="s">
-        <v>113</v>
-      </c>
-      <c r="C133" t="s">
-        <v>114</v>
-      </c>
-      <c r="D133" t="s">
-        <v>115</v>
-      </c>
-      <c r="E133" t="s">
-        <v>116</v>
-      </c>
-      <c r="F133">
-        <v>2</v>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I133" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>45711</v>
+        <v>45928</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E134" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -4309,68 +4722,77 @@
       <c r="H134" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I134" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>45708</v>
+        <v>45931</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="E135" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="1">
+        <v>45934</v>
+      </c>
+      <c r="B136" t="s">
+        <v>87</v>
+      </c>
+      <c r="C136" t="s">
+        <v>14</v>
+      </c>
+      <c r="D136" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A136" s="1">
-        <v>45703</v>
-      </c>
-      <c r="B136" t="s">
-        <v>117</v>
-      </c>
-      <c r="C136" t="s">
-        <v>68</v>
-      </c>
-      <c r="D136" t="s">
-        <v>69</v>
-      </c>
-      <c r="E136" t="s">
-        <v>70</v>
-      </c>
-      <c r="F136">
-        <v>1</v>
-      </c>
-      <c r="G136">
-        <v>1</v>
-      </c>
-      <c r="H136" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I136" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
-        <v>45700</v>
+        <v>45945</v>
       </c>
       <c r="B137" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D137" t="s">
         <v>51</v>
@@ -4379,7 +4801,7 @@
         <v>52</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -4387,322 +4809,361 @@
       <c r="H137" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I137" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
-        <v>45697</v>
+        <v>45949</v>
       </c>
       <c r="B138" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="C138" t="s">
+        <v>14</v>
+      </c>
+      <c r="D138" t="s">
+        <v>94</v>
+      </c>
+      <c r="E138" t="s">
+        <v>95</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>2</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" s="1">
+        <v>45956</v>
+      </c>
+      <c r="B139" t="s">
+        <v>87</v>
+      </c>
+      <c r="C139" t="s">
+        <v>14</v>
+      </c>
+      <c r="D139" t="s">
+        <v>92</v>
+      </c>
+      <c r="E139" t="s">
+        <v>93</v>
+      </c>
+      <c r="F139">
+        <v>2</v>
+      </c>
+      <c r="G139">
+        <v>2</v>
+      </c>
+      <c r="H139" t="s">
+        <v>28</v>
+      </c>
+      <c r="I139" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B140" t="s">
+        <v>87</v>
+      </c>
+      <c r="C140" t="s">
+        <v>14</v>
+      </c>
+      <c r="D140" t="s">
+        <v>90</v>
+      </c>
+      <c r="E140" t="s">
+        <v>91</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140" t="s">
+        <v>28</v>
+      </c>
+      <c r="I140" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" s="1">
+        <v>45966</v>
+      </c>
+      <c r="B141" t="s">
+        <v>87</v>
+      </c>
+      <c r="C141" t="s">
+        <v>14</v>
+      </c>
+      <c r="D141" t="s">
+        <v>31</v>
+      </c>
+      <c r="E141" t="s">
+        <v>32</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>3</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" s="1">
+        <v>45970</v>
+      </c>
+      <c r="B142" t="s">
+        <v>87</v>
+      </c>
+      <c r="C142" t="s">
+        <v>14</v>
+      </c>
+      <c r="D142" t="s">
+        <v>26</v>
+      </c>
+      <c r="E142" t="s">
+        <v>27</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142" t="s">
+        <v>28</v>
+      </c>
+      <c r="I142" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" s="1">
+        <v>45979</v>
+      </c>
+      <c r="B143" t="s">
+        <v>87</v>
+      </c>
+      <c r="C143" t="s">
+        <v>14</v>
+      </c>
+      <c r="D143" t="s">
+        <v>88</v>
+      </c>
+      <c r="E143" t="s">
+        <v>89</v>
+      </c>
+      <c r="F143">
+        <v>2</v>
+      </c>
+      <c r="G143">
+        <v>3</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" s="1">
+        <v>45983</v>
+      </c>
+      <c r="B144" t="s">
+        <v>87</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144" t="s">
+        <v>41</v>
+      </c>
+      <c r="E144" t="s">
+        <v>42</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144">
+        <v>3</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" s="1">
+        <v>45991</v>
+      </c>
+      <c r="B145" t="s">
+        <v>87</v>
+      </c>
+      <c r="C145" t="s">
+        <v>14</v>
+      </c>
+      <c r="D145" t="s">
+        <v>45</v>
+      </c>
+      <c r="E145" t="s">
+        <v>46</v>
+      </c>
+      <c r="F145">
+        <v>2</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="H145" t="s">
+        <v>28</v>
+      </c>
+      <c r="I145" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" s="1">
+        <v>45995</v>
+      </c>
+      <c r="B146" t="s">
+        <v>87</v>
+      </c>
+      <c r="C146" t="s">
+        <v>14</v>
+      </c>
+      <c r="D146" t="s">
+        <v>59</v>
+      </c>
+      <c r="E146" t="s">
+        <v>60</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+      <c r="G146">
+        <v>2</v>
+      </c>
+      <c r="H146" t="s">
+        <v>28</v>
+      </c>
+      <c r="I146" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" s="1">
+        <v>45998</v>
+      </c>
+      <c r="B147" t="s">
+        <v>87</v>
+      </c>
+      <c r="C147" t="s">
+        <v>14</v>
+      </c>
+      <c r="D147" t="s">
+        <v>47</v>
+      </c>
+      <c r="E147" t="s">
+        <v>48</v>
+      </c>
+      <c r="F147">
+        <v>2</v>
+      </c>
+      <c r="G147">
+        <v>4</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B148" t="s">
+        <v>126</v>
+      </c>
+      <c r="C148" t="s">
         <v>68</v>
       </c>
-      <c r="D138" t="s">
-        <v>85</v>
-      </c>
-      <c r="E138" t="s">
-        <v>86</v>
-      </c>
-      <c r="F138">
-        <v>2</v>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A139" s="1">
-        <v>45694</v>
-      </c>
-      <c r="B139" t="s">
-        <v>117</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="D148" t="s">
+        <v>81</v>
+      </c>
+      <c r="E148" t="s">
+        <v>82</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>2</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B149" t="s">
+        <v>126</v>
+      </c>
+      <c r="C149" t="s">
         <v>68</v>
       </c>
-      <c r="D139" t="s">
-        <v>79</v>
-      </c>
-      <c r="E139" t="s">
-        <v>80</v>
-      </c>
-      <c r="F139">
-        <v>0</v>
-      </c>
-      <c r="G139">
-        <v>1</v>
-      </c>
-      <c r="H139" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A140" s="1">
-        <v>45690</v>
-      </c>
-      <c r="B140" t="s">
-        <v>118</v>
-      </c>
-      <c r="C140" t="s">
-        <v>119</v>
-      </c>
-      <c r="D140" t="s">
-        <v>51</v>
-      </c>
-      <c r="E140" t="s">
-        <v>52</v>
-      </c>
-      <c r="F140">
-        <v>3</v>
-      </c>
-      <c r="G140">
-        <v>1</v>
-      </c>
-      <c r="H140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A141" s="1">
-        <v>45686</v>
-      </c>
-      <c r="B141" t="s">
-        <v>117</v>
-      </c>
-      <c r="C141" t="s">
-        <v>68</v>
-      </c>
-      <c r="D141" t="s">
-        <v>43</v>
-      </c>
-      <c r="E141" t="s">
-        <v>44</v>
-      </c>
-      <c r="F141">
-        <v>1</v>
-      </c>
-      <c r="G141">
-        <v>2</v>
-      </c>
-      <c r="H141" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A142" s="1">
-        <v>45683</v>
-      </c>
-      <c r="B142" t="s">
-        <v>117</v>
-      </c>
-      <c r="C142" t="s">
-        <v>68</v>
-      </c>
-      <c r="D142" t="s">
-        <v>83</v>
-      </c>
-      <c r="E142" t="s">
-        <v>84</v>
-      </c>
-      <c r="F142">
-        <v>0</v>
-      </c>
-      <c r="G142">
-        <v>2</v>
-      </c>
-      <c r="H142" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A143" s="1">
-        <v>45679</v>
-      </c>
-      <c r="B143" t="s">
-        <v>117</v>
-      </c>
-      <c r="C143" t="s">
-        <v>68</v>
-      </c>
-      <c r="D143" t="s">
-        <v>77</v>
-      </c>
-      <c r="E143" t="s">
-        <v>78</v>
-      </c>
-      <c r="F143">
-        <v>2</v>
-      </c>
-      <c r="G143">
-        <v>1</v>
-      </c>
-      <c r="H143" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A144" s="1">
-        <v>45675</v>
-      </c>
-      <c r="B144" t="s">
-        <v>117</v>
-      </c>
-      <c r="C144" t="s">
-        <v>68</v>
-      </c>
-      <c r="D144" t="s">
+      <c r="D149" t="s">
         <v>71</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E149" t="s">
         <v>72</v>
       </c>
-      <c r="F144">
-        <v>2</v>
-      </c>
-      <c r="G144">
-        <v>1</v>
-      </c>
-      <c r="H144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A145" s="1">
-        <v>45671</v>
-      </c>
-      <c r="B145" t="s">
-        <v>117</v>
-      </c>
-      <c r="C145" t="s">
-        <v>68</v>
-      </c>
-      <c r="D145" t="s">
-        <v>81</v>
-      </c>
-      <c r="E145" t="s">
-        <v>82</v>
-      </c>
-      <c r="F145">
-        <v>0</v>
-      </c>
-      <c r="G145">
-        <v>2</v>
-      </c>
-      <c r="H145" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A146" s="1">
-        <v>45668</v>
-      </c>
-      <c r="B146" t="s">
-        <v>117</v>
-      </c>
-      <c r="C146" t="s">
-        <v>68</v>
-      </c>
-      <c r="D146" t="s">
-        <v>120</v>
-      </c>
-      <c r="E146" t="s">
-        <v>121</v>
-      </c>
-      <c r="F146">
-        <v>2</v>
-      </c>
-      <c r="G146">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A147" s="1">
-        <v>46099</v>
-      </c>
-      <c r="B147" t="s">
-        <v>122</v>
-      </c>
-      <c r="C147" t="s">
-        <v>14</v>
-      </c>
-      <c r="D147" t="s">
-        <v>24</v>
-      </c>
-      <c r="E147" t="s">
-        <v>25</v>
-      </c>
-      <c r="F147">
-        <v>2</v>
-      </c>
-      <c r="G147">
-        <v>1</v>
-      </c>
-      <c r="H147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A148" s="1">
-        <v>46095</v>
-      </c>
-      <c r="B148" t="s">
-        <v>122</v>
-      </c>
-      <c r="C148" t="s">
-        <v>14</v>
-      </c>
-      <c r="D148" t="s">
-        <v>51</v>
-      </c>
-      <c r="E148" t="s">
-        <v>52</v>
-      </c>
-      <c r="F148">
-        <v>3</v>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A149" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B149" t="s">
-        <v>123</v>
-      </c>
-      <c r="C149" t="s">
-        <v>21</v>
-      </c>
-      <c r="D149" t="s">
-        <v>124</v>
-      </c>
-      <c r="E149" t="s">
-        <v>125</v>
-      </c>
       <c r="F149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I149" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
-        <v>46088</v>
+        <v>46043</v>
       </c>
       <c r="B150" t="s">
         <v>126</v>
@@ -4711,143 +5172,158 @@
         <v>68</v>
       </c>
       <c r="D150" t="s">
+        <v>77</v>
+      </c>
+      <c r="E150" t="s">
+        <v>78</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B151" t="s">
+        <v>126</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
         <v>83</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E151" t="s">
         <v>84</v>
       </c>
-      <c r="F150">
-        <v>1</v>
-      </c>
-      <c r="G150">
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>2</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B152" t="s">
+        <v>122</v>
+      </c>
+      <c r="C152" t="s">
+        <v>14</v>
+      </c>
+      <c r="D152" t="s">
+        <v>59</v>
+      </c>
+      <c r="E152" t="s">
+        <v>60</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>4</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B153" t="s">
+        <v>126</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>43</v>
+      </c>
+      <c r="E153" t="s">
+        <v>44</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B154" t="s">
+        <v>122</v>
+      </c>
+      <c r="C154" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" t="s">
+        <v>41</v>
+      </c>
+      <c r="E154" t="s">
+        <v>42</v>
+      </c>
+      <c r="F154">
+        <v>5</v>
+      </c>
+      <c r="G154">
         <v>3</v>
       </c>
-      <c r="H150" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A151" s="1">
-        <v>46084</v>
-      </c>
-      <c r="B151" t="s">
-        <v>123</v>
-      </c>
-      <c r="C151" t="s">
-        <v>21</v>
-      </c>
-      <c r="D151" t="s">
-        <v>124</v>
-      </c>
-      <c r="E151" t="s">
-        <v>125</v>
-      </c>
-      <c r="F151">
-        <v>1</v>
-      </c>
-      <c r="G151">
-        <v>1</v>
-      </c>
-      <c r="H151" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A152" s="1">
-        <v>46081</v>
-      </c>
-      <c r="B152" t="s">
+      <c r="H154" t="s">
+        <v>12</v>
+      </c>
+      <c r="I154" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="1">
+        <v>46061</v>
+      </c>
+      <c r="B155" t="s">
         <v>126</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C155" t="s">
         <v>68</v>
       </c>
-      <c r="D152" t="s">
-        <v>69</v>
-      </c>
-      <c r="E152" t="s">
-        <v>70</v>
-      </c>
-      <c r="F152">
-        <v>0</v>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A153" s="1">
-        <v>46078</v>
-      </c>
-      <c r="B153" t="s">
-        <v>123</v>
-      </c>
-      <c r="C153" t="s">
-        <v>21</v>
-      </c>
-      <c r="D153" t="s">
-        <v>127</v>
-      </c>
-      <c r="E153" t="s">
-        <v>128</v>
-      </c>
-      <c r="F153">
-        <v>0</v>
-      </c>
-      <c r="G153">
-        <v>2</v>
-      </c>
-      <c r="H153" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A154" s="1">
-        <v>46074</v>
-      </c>
-      <c r="B154" t="s">
-        <v>126</v>
-      </c>
-      <c r="C154" t="s">
-        <v>68</v>
-      </c>
-      <c r="D154" t="s">
-        <v>69</v>
-      </c>
-      <c r="E154" t="s">
-        <v>70</v>
-      </c>
-      <c r="F154">
-        <v>0</v>
-      </c>
-      <c r="G154">
-        <v>2</v>
-      </c>
-      <c r="H154" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A155" s="1">
-        <v>46071</v>
-      </c>
-      <c r="B155" t="s">
-        <v>123</v>
-      </c>
-      <c r="C155" t="s">
-        <v>21</v>
-      </c>
       <c r="D155" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="E155" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -4855,77 +5331,86 @@
       <c r="H155" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I155" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
-        <v>46068</v>
+        <v>46065</v>
       </c>
       <c r="B156" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C156" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D156" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E156" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I156" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>46065</v>
+        <v>46068</v>
       </c>
       <c r="B157" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C157" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D157" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E157" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I157" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>46061</v>
+        <v>46071</v>
       </c>
       <c r="B158" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C158" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D158" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="E158" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="F158">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -4933,114 +5418,129 @@
       <c r="H158" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I158" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>46057</v>
+        <v>46074</v>
       </c>
       <c r="B159" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C159" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D159" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E159" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F159">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H159" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I159" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
-        <v>46054</v>
+        <v>46078</v>
       </c>
       <c r="B160" t="s">
+        <v>123</v>
+      </c>
+      <c r="C160" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" t="s">
+        <v>127</v>
+      </c>
+      <c r="E160" t="s">
+        <v>128</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A161" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B161" t="s">
         <v>126</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C161" t="s">
         <v>68</v>
       </c>
-      <c r="D160" t="s">
-        <v>43</v>
-      </c>
-      <c r="E160" t="s">
-        <v>44</v>
-      </c>
-      <c r="F160">
-        <v>1</v>
-      </c>
-      <c r="G160">
-        <v>0</v>
-      </c>
-      <c r="H160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A161" s="1">
-        <v>46051</v>
-      </c>
-      <c r="B161" t="s">
-        <v>122</v>
-      </c>
-      <c r="C161" t="s">
-        <v>14</v>
-      </c>
       <c r="D161" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E161" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F161">
         <v>0</v>
       </c>
       <c r="G161">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H161" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I161" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
-        <v>46046</v>
+        <v>46084</v>
       </c>
       <c r="B162" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C162" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D162" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="E162" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H162" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="I162" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
-        <v>46043</v>
+        <v>46088</v>
       </c>
       <c r="B163" t="s">
         <v>126</v>
@@ -5049,76 +5549,85 @@
         <v>68</v>
       </c>
       <c r="D163" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E163" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I163" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
-        <v>46040</v>
+        <v>46091</v>
       </c>
       <c r="B164" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C164" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D164" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E164" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="F164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I164" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
-        <v>46037</v>
+        <v>46095</v>
       </c>
       <c r="B165" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C165" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D165" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E165" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H165" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I165" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
-        <v>46124</v>
+        <v>46099</v>
       </c>
       <c r="B166" t="s">
         <v>122</v>
@@ -5127,50 +5636,56 @@
         <v>14</v>
       </c>
       <c r="D166" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E166" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="F166">
         <v>2</v>
       </c>
       <c r="G166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H166" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I166" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
-        <v>46121</v>
+        <v>46102</v>
       </c>
       <c r="B167" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C167" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="D167" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="E167" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="F167">
         <v>1</v>
       </c>
       <c r="G167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H167" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I167" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
-        <v>46116</v>
+        <v>46110</v>
       </c>
       <c r="B168" t="s">
         <v>122</v>
@@ -5179,22 +5694,25 @@
         <v>14</v>
       </c>
       <c r="D168" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E168" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H168" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="I168" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>46113</v>
       </c>
@@ -5219,10 +5737,13 @@
       <c r="H169" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I169" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
-        <v>46110</v>
+        <v>46116</v>
       </c>
       <c r="B170" t="s">
         <v>122</v>
@@ -5231,49 +5752,84 @@
         <v>14</v>
       </c>
       <c r="D170" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E170" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F170">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H170" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
-        <v>46102</v>
+        <v>46121</v>
       </c>
       <c r="B171" t="s">
+        <v>131</v>
+      </c>
+      <c r="C171" t="s">
+        <v>114</v>
+      </c>
+      <c r="D171" t="s">
+        <v>132</v>
+      </c>
+      <c r="E171" t="s">
+        <v>133</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>28</v>
+      </c>
+      <c r="I171" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A172" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B172" t="s">
         <v>122</v>
       </c>
-      <c r="C171" t="s">
-        <v>14</v>
-      </c>
-      <c r="D171" t="s">
-        <v>35</v>
-      </c>
-      <c r="E171" t="s">
-        <v>36</v>
-      </c>
-      <c r="F171">
-        <v>1</v>
-      </c>
-      <c r="G171">
-        <v>2</v>
-      </c>
-      <c r="H171" t="s">
-        <v>17</v>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+      <c r="D172" t="s">
+        <v>129</v>
+      </c>
+      <c r="E172" t="s">
+        <v>130</v>
+      </c>
+      <c r="F172">
+        <v>2</v>
+      </c>
+      <c r="G172">
+        <v>2</v>
+      </c>
+      <c r="H172" t="s">
+        <v>28</v>
+      </c>
+      <c r="I172" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H171" xr:uid="{2BBC53B6-4B60-44A2-8CF3-BAC076789A26}"/>
+  <autoFilter ref="A1:I172" xr:uid="{2BBC53B6-4B60-44A2-8CF3-BAC076789A26}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/dPlacares.xlsx
+++ b/dPlacares.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="519" documentId="8_{F813B61F-9670-42F1-8555-B78B55D4625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{772E36AA-D24A-4619-8D5B-AA3734D1ECE3}"/>
+  <xr:revisionPtr revIDLastSave="620" documentId="8_{F813B61F-9670-42F1-8555-B78B55D4625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2B64E6-6360-4B4B-91F4-2044E30E0875}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6666F575-2A8C-4CCA-9598-CF178E39A238}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="147">
   <si>
     <t>Data</t>
   </si>
@@ -453,6 +453,33 @@
   </si>
   <si>
     <t>c</t>
+  </si>
+  <si>
+    <t>Copa do Brasil 2026</t>
+  </si>
+  <si>
+    <t>Independiente Petrolero</t>
+  </si>
+  <si>
+    <t>124IPBOSU</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>29CHBRSC</t>
+  </si>
+  <si>
+    <t>Racing</t>
+  </si>
+  <si>
+    <t>Atlético-MG</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>35REBRPA</t>
   </si>
 </sst>
 </file>
@@ -488,11 +515,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -827,13 +852,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BBC53B6-4B60-44A2-8CF3-BAC076789A26}">
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.90625" bestFit="1" customWidth="1"/>
@@ -1044,7 +1069,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>45616</v>
       </c>
       <c r="B8" t="s">
@@ -1073,7 +1098,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>45605</v>
       </c>
       <c r="B9" t="s">
@@ -1102,7 +1127,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
+      <c r="A10" s="1">
         <v>45601</v>
       </c>
       <c r="B10" t="s">
@@ -1131,7 +1156,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>45595</v>
       </c>
       <c r="B11" t="s">
@@ -1160,7 +1185,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>45591</v>
       </c>
       <c r="B12" t="s">
@@ -1184,12 +1209,12 @@
       <c r="H12" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>45588</v>
       </c>
       <c r="B13" t="s">
@@ -1218,7 +1243,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>45583</v>
       </c>
       <c r="B14" t="s">
@@ -1247,7 +1272,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>45570</v>
       </c>
       <c r="B15" t="s">
@@ -1271,12 +1296,12 @@
       <c r="H15" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>45563</v>
       </c>
       <c r="B16" t="s">
@@ -1300,12 +1325,12 @@
       <c r="H16" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>45560</v>
       </c>
       <c r="B17" t="s">
@@ -1329,12 +1354,12 @@
       <c r="H17" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>45556</v>
       </c>
       <c r="B18" t="s">
@@ -1358,12 +1383,12 @@
       <c r="H18" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>45553</v>
       </c>
       <c r="B19" t="s">
@@ -1387,12 +1412,12 @@
       <c r="H19" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>45549</v>
       </c>
       <c r="B20" t="s">
@@ -1416,12 +1441,12 @@
       <c r="H20" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>45535</v>
       </c>
       <c r="B21" t="s">
@@ -1445,12 +1470,12 @@
       <c r="H21" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>45529</v>
       </c>
       <c r="B22" t="s">
@@ -1474,12 +1499,12 @@
       <c r="H22" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>45525</v>
       </c>
       <c r="B23" t="s">
@@ -1503,12 +1528,12 @@
       <c r="H23" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>45522</v>
       </c>
       <c r="B24" t="s">
@@ -1532,12 +1557,12 @@
       <c r="H24" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>45518</v>
       </c>
       <c r="B25" t="s">
@@ -1561,12 +1586,12 @@
       <c r="H25" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
+      <c r="A26" s="1">
         <v>45515</v>
       </c>
       <c r="B26" t="s">
@@ -1590,12 +1615,12 @@
       <c r="H26" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>45511</v>
       </c>
       <c r="B27" t="s">
@@ -1619,12 +1644,12 @@
       <c r="H27" t="s">
         <v>12</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>45507</v>
       </c>
       <c r="B28" t="s">
@@ -1648,12 +1673,12 @@
       <c r="H28" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>45503</v>
       </c>
       <c r="B29" t="s">
@@ -1677,12 +1702,12 @@
       <c r="H29" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>45500</v>
       </c>
       <c r="B30" t="s">
@@ -1706,12 +1731,12 @@
       <c r="H30" t="s">
         <v>12</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>45497</v>
       </c>
       <c r="B31" t="s">
@@ -1735,12 +1760,12 @@
       <c r="H31" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>45493</v>
       </c>
       <c r="B32" t="s">
@@ -1764,12 +1789,12 @@
       <c r="H32" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>45490</v>
       </c>
       <c r="B33" t="s">
@@ -1793,12 +1818,12 @@
       <c r="H33" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>45484</v>
       </c>
       <c r="B34" t="s">
@@ -1822,12 +1847,12 @@
       <c r="H34" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>45480</v>
       </c>
       <c r="B35" t="s">
@@ -1851,12 +1876,12 @@
       <c r="H35" t="s">
         <v>17</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>45476</v>
       </c>
       <c r="B36" t="s">
@@ -1880,12 +1905,12 @@
       <c r="H36" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>45472</v>
       </c>
       <c r="B37" t="s">
@@ -1909,12 +1934,12 @@
       <c r="H37" t="s">
         <v>28</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
+      <c r="A38" s="1">
         <v>45469</v>
       </c>
       <c r="B38" t="s">
@@ -1938,12 +1963,12 @@
       <c r="H38" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>45465</v>
       </c>
       <c r="B39" t="s">
@@ -1967,12 +1992,12 @@
       <c r="H39" t="s">
         <v>12</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
+      <c r="A40" s="1">
         <v>45462</v>
       </c>
       <c r="B40" t="s">
@@ -1996,12 +2021,12 @@
       <c r="H40" t="s">
         <v>28</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>45459</v>
       </c>
       <c r="B41" t="s">
@@ -2025,12 +2050,12 @@
       <c r="H41" t="s">
         <v>17</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>45454</v>
       </c>
       <c r="B42" t="s">
@@ -2059,7 +2084,7 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>45444</v>
       </c>
       <c r="B43" t="s">
@@ -2088,7 +2113,7 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>45440</v>
       </c>
       <c r="B44" t="s">
@@ -2117,7 +2142,7 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>45434</v>
       </c>
       <c r="B45" t="s">
@@ -2146,7 +2171,7 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>45428</v>
       </c>
       <c r="B46" t="s">
@@ -2175,7 +2200,7 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>45424</v>
       </c>
       <c r="B47" t="s">
@@ -2204,7 +2229,7 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>45420</v>
       </c>
       <c r="B48" t="s">
@@ -2233,7 +2258,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>45417</v>
       </c>
       <c r="B49" t="s">
@@ -2262,7 +2287,7 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
+      <c r="A50" s="1">
         <v>45414</v>
       </c>
       <c r="B50" t="s">
@@ -2291,7 +2316,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
+      <c r="A51" s="1">
         <v>45410</v>
       </c>
       <c r="B51" t="s">
@@ -2315,12 +2340,12 @@
       <c r="H51" t="s">
         <v>17</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A52" s="2">
+      <c r="A52" s="1">
         <v>45406</v>
       </c>
       <c r="B52" t="s">
@@ -2349,7 +2374,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A53" s="2">
+      <c r="A53" s="1">
         <v>45403</v>
       </c>
       <c r="B53" t="s">
@@ -2378,7 +2403,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A54" s="2">
+      <c r="A54" s="1">
         <v>45400</v>
       </c>
       <c r="B54" t="s">
@@ -2407,7 +2432,7 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+      <c r="A55" s="1">
         <v>45393</v>
       </c>
       <c r="B55" t="s">
@@ -2431,12 +2456,12 @@
       <c r="H55" t="s">
         <v>12</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="I55" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>45385</v>
       </c>
       <c r="B56" t="s">
@@ -2460,12 +2485,12 @@
       <c r="H56" t="s">
         <v>12</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A57" s="2">
+      <c r="A57" s="1">
         <v>45382</v>
       </c>
       <c r="B57" t="s">
@@ -2489,12 +2514,12 @@
       <c r="H57" t="s">
         <v>17</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A58" s="2">
+      <c r="A58" s="1">
         <v>45378</v>
       </c>
       <c r="B58" t="s">
@@ -2518,12 +2543,12 @@
       <c r="H58" t="s">
         <v>17</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A59" s="2">
+      <c r="A59" s="1">
         <v>45368</v>
       </c>
       <c r="B59" t="s">
@@ -2547,12 +2572,12 @@
       <c r="H59" t="s">
         <v>17</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A60" s="2">
+      <c r="A60" s="1">
         <v>45365</v>
       </c>
       <c r="B60" t="s">
@@ -2576,12 +2601,12 @@
       <c r="H60" t="s">
         <v>12</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="I60" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A61" s="2">
+      <c r="A61" s="1">
         <v>45364</v>
       </c>
       <c r="B61" t="s">
@@ -2605,12 +2630,12 @@
       <c r="H61" t="s">
         <v>28</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="I61" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="2">
+      <c r="A62" s="1">
         <v>45361</v>
       </c>
       <c r="B62" t="s">
@@ -2634,12 +2659,12 @@
       <c r="H62" t="s">
         <v>17</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I62" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>45357</v>
       </c>
       <c r="B63" t="s">
@@ -2663,12 +2688,12 @@
       <c r="H63" t="s">
         <v>17</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A64" s="2">
+      <c r="A64" s="1">
         <v>45354</v>
       </c>
       <c r="B64" t="s">
@@ -2692,12 +2717,12 @@
       <c r="H64" t="s">
         <v>17</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A65" s="2">
+      <c r="A65" s="1">
         <v>45350</v>
       </c>
       <c r="B65" t="s">
@@ -2721,12 +2746,12 @@
       <c r="H65" t="s">
         <v>17</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A66" s="2">
+      <c r="A66" s="1">
         <v>45346</v>
       </c>
       <c r="B66" t="s">
@@ -2750,12 +2775,12 @@
       <c r="H66" t="s">
         <v>17</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I66" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" s="2">
+      <c r="A67" s="1">
         <v>45343</v>
       </c>
       <c r="B67" t="s">
@@ -2779,12 +2804,12 @@
       <c r="H67" t="s">
         <v>28</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" s="2">
+      <c r="A68" s="1">
         <v>45340</v>
       </c>
       <c r="B68" t="s">
@@ -2808,12 +2833,12 @@
       <c r="H68" t="s">
         <v>12</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A69" s="2">
+      <c r="A69" s="1">
         <v>45336</v>
       </c>
       <c r="B69" t="s">
@@ -2837,12 +2862,12 @@
       <c r="H69" t="s">
         <v>17</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A70" s="2">
+      <c r="A70" s="1">
         <v>45329</v>
       </c>
       <c r="B70" t="s">
@@ -2866,12 +2891,12 @@
       <c r="H70" t="s">
         <v>12</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I70" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" s="2">
+      <c r="A71" s="1">
         <v>45325</v>
       </c>
       <c r="B71" t="s">
@@ -2895,12 +2920,12 @@
       <c r="H71" t="s">
         <v>28</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="I71" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" s="2">
+      <c r="A72" s="1">
         <v>45321</v>
       </c>
       <c r="B72" t="s">
@@ -2924,12 +2949,12 @@
       <c r="H72" t="s">
         <v>28</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I72" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" s="2">
+      <c r="A73" s="1">
         <v>45318</v>
       </c>
       <c r="B73" t="s">
@@ -2953,12 +2978,12 @@
       <c r="H73" t="s">
         <v>17</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="I73" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" s="2">
+      <c r="A74" s="1">
         <v>45315</v>
       </c>
       <c r="B74" t="s">
@@ -2982,12 +3007,12 @@
       <c r="H74" t="s">
         <v>12</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I74" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A75" s="2">
+      <c r="A75" s="1">
         <v>45311</v>
       </c>
       <c r="B75" t="s">
@@ -3011,12 +3036,12 @@
       <c r="H75" t="s">
         <v>17</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A76" s="2">
+      <c r="A76" s="1">
         <v>45308</v>
       </c>
       <c r="B76" t="s">
@@ -3040,7 +3065,7 @@
       <c r="H76" t="s">
         <v>17</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3712,7 +3737,7 @@
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A100" s="2">
+      <c r="A100" s="1">
         <v>45775</v>
       </c>
       <c r="B100" t="s">
@@ -4001,7 +4026,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="110" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>45812</v>
       </c>
@@ -4030,7 +4055,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="111" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>45823</v>
       </c>
@@ -4059,7 +4084,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="112" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>45827</v>
       </c>
@@ -4088,7 +4113,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="113" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>45831</v>
       </c>
@@ -4117,7 +4142,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="114" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>45836</v>
       </c>
@@ -4146,7 +4171,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="115" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>45850</v>
       </c>
@@ -4175,7 +4200,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="116" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>45854</v>
       </c>
@@ -4204,7 +4229,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="117" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>45858</v>
       </c>
@@ -4233,7 +4258,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="118" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>45864</v>
       </c>
@@ -4262,7 +4287,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="119" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>45867</v>
       </c>
@@ -4291,7 +4316,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="120" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>45872</v>
       </c>
@@ -4320,7 +4345,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="121" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>45875</v>
       </c>
@@ -4349,7 +4374,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="122" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>45878</v>
       </c>
@@ -4378,7 +4403,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="123" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>45883</v>
       </c>
@@ -4407,7 +4432,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="124" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>45886</v>
       </c>
@@ -4436,7 +4461,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="125" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>45890</v>
       </c>
@@ -4465,7 +4490,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="126" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>45893</v>
       </c>
@@ -4494,7 +4519,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="127" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>45896</v>
       </c>
@@ -4523,7 +4548,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="128" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>45899</v>
       </c>
@@ -4552,7 +4577,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="129" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>45911</v>
       </c>
@@ -4581,7 +4606,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="130" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>45914</v>
       </c>
@@ -4610,7 +4635,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="131" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>45917</v>
       </c>
@@ -4639,7 +4664,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="132" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>45920</v>
       </c>
@@ -4668,7 +4693,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="133" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>45924</v>
       </c>
@@ -4697,7 +4722,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="134" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>45928</v>
       </c>
@@ -4726,7 +4751,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="135" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>45931</v>
       </c>
@@ -4755,7 +4780,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="136" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>45934</v>
       </c>
@@ -4784,7 +4809,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>45945</v>
       </c>
@@ -4813,7 +4838,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>45949</v>
       </c>
@@ -5161,7 +5186,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="150" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>46043</v>
       </c>
@@ -5190,7 +5215,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="151" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>46046</v>
       </c>
@@ -5219,7 +5244,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="152" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>46051</v>
       </c>
@@ -5248,7 +5273,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="153" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>46054</v>
       </c>
@@ -5277,7 +5302,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="154" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>46057</v>
       </c>
@@ -5306,7 +5331,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="155" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>46061</v>
       </c>
@@ -5826,6 +5851,325 @@
       </c>
       <c r="I172" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A173" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B173" t="s">
+        <v>131</v>
+      </c>
+      <c r="C173" t="s">
+        <v>114</v>
+      </c>
+      <c r="D173" t="s">
+        <v>143</v>
+      </c>
+      <c r="E173" t="s">
+        <v>116</v>
+      </c>
+      <c r="F173">
+        <v>2</v>
+      </c>
+      <c r="G173">
+        <v>3</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A174" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B174" t="s">
+        <v>122</v>
+      </c>
+      <c r="C174" t="s">
+        <v>14</v>
+      </c>
+      <c r="D174" t="s">
+        <v>141</v>
+      </c>
+      <c r="E174" t="s">
+        <v>142</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="G174">
+        <v>4</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A175" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B175" t="s">
+        <v>138</v>
+      </c>
+      <c r="C175" t="s">
+        <v>56</v>
+      </c>
+      <c r="D175" t="s">
+        <v>141</v>
+      </c>
+      <c r="E175" t="s">
+        <v>142</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A176" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B176" t="s">
+        <v>122</v>
+      </c>
+      <c r="C176" t="s">
+        <v>14</v>
+      </c>
+      <c r="D176" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" t="s">
+        <v>19</v>
+      </c>
+      <c r="F176">
+        <v>2</v>
+      </c>
+      <c r="G176">
+        <v>2</v>
+      </c>
+      <c r="H176" t="s">
+        <v>28</v>
+      </c>
+      <c r="I176" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A177" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B177" t="s">
+        <v>131</v>
+      </c>
+      <c r="C177" t="s">
+        <v>114</v>
+      </c>
+      <c r="D177" t="s">
+        <v>139</v>
+      </c>
+      <c r="E177" t="s">
+        <v>140</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+      <c r="G177">
+        <v>3</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A178" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B178" t="s">
+        <v>122</v>
+      </c>
+      <c r="C178" t="s">
+        <v>14</v>
+      </c>
+      <c r="D178" t="s">
+        <v>145</v>
+      </c>
+      <c r="E178" t="s">
+        <v>146</v>
+      </c>
+      <c r="F178">
+        <v>2</v>
+      </c>
+      <c r="G178">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A179" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B179" t="s">
+        <v>131</v>
+      </c>
+      <c r="C179" t="s">
+        <v>114</v>
+      </c>
+      <c r="D179" t="s">
+        <v>143</v>
+      </c>
+      <c r="E179" t="s">
+        <v>116</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>2</v>
+      </c>
+      <c r="H179" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A180" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B180" t="s">
+        <v>122</v>
+      </c>
+      <c r="C180" t="s">
+        <v>14</v>
+      </c>
+      <c r="D180" t="s">
+        <v>144</v>
+      </c>
+      <c r="E180" t="s">
+        <v>23</v>
+      </c>
+      <c r="F180">
+        <v>1</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>28</v>
+      </c>
+      <c r="I180" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A181" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B181" t="s">
+        <v>138</v>
+      </c>
+      <c r="C181" t="s">
+        <v>56</v>
+      </c>
+      <c r="D181" t="s">
+        <v>141</v>
+      </c>
+      <c r="E181" t="s">
+        <v>142</v>
+      </c>
+      <c r="F181">
+        <v>2</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181" t="s">
+        <v>12</v>
+      </c>
+      <c r="I181" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A182" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B182" t="s">
+        <v>122</v>
+      </c>
+      <c r="C182" t="s">
+        <v>14</v>
+      </c>
+      <c r="D182" t="s">
+        <v>45</v>
+      </c>
+      <c r="E182" t="s">
+        <v>46</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+      <c r="G182">
+        <v>3</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A183" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B183" t="s">
+        <v>131</v>
+      </c>
+      <c r="C183" t="s">
+        <v>114</v>
+      </c>
+      <c r="D183" t="s">
+        <v>139</v>
+      </c>
+      <c r="E183" t="s">
+        <v>140</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>3</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
